--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_367_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_367_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2459</v>
+        <v>2.0842</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9991</v>
+        <v>0.1734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2468</v>
+        <v>1.9108</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8035</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8897</v>
+        <v>1.728</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6201</v>
+        <v>0.7945</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2696</v>
+        <v>0.9335</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8297</v>
+        <v>1.272</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6202</v>
+        <v>1.2978</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2095</v>
+        <v>-0.0257</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6244</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0108</v>
+        <v>0.4531</v>
       </c>
       <c r="T3" t="n">
-        <v>0.999</v>
+        <v>0.6765</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0119</v>
+        <v>-0.2234</v>
       </c>
       <c r="V3" t="n">
         <v>0.2836</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1659</v>
+        <v>0.8057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3837</v>
+        <v>0.8555</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2178</v>
+        <v>-0.0498</v>
       </c>
       <c r="G4" t="n">
         <v>-1.5059</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5601</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.963</v>
+        <v>-0.4911</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4028</v>
+        <v>0.5709</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2763</v>
+        <v>-0.2676</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3705</v>
+        <v>0.6045</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9058</v>
+        <v>-0.8722</v>
       </c>
       <c r="G5" t="n">
         <v>-3.7708</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3431</v>
+        <v>0.6655</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5342</v>
+        <v>0.4408</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1911</v>
+        <v>0.2247</v>
       </c>
       <c r="V5" t="n">
         <v>1.214</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4374</v>
+        <v>-1.4037</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9768</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4606</v>
+        <v>-0.427</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3104</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T6" t="n">
         <v>-0.224</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1792</v>
+        <v>-2.704</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9272</v>
+        <v>-1.4856</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.252</v>
+        <v>-1.2184</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0089</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4353</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9911</v>
+        <v>0.4327</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5557</v>
+        <v>-0.5221</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8093</v>
+        <v>-3.0611</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9176</v>
+        <v>-2.5167</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8917</v>
+        <v>-0.5444</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.526</v>
+        <v>-6.5982</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7899</v>
+        <v>-1.8368</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7361</v>
+        <v>-4.7614</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2534</v>
+        <v>-4.371</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2534</v>
+        <v>-1.1386</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-3.2324</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2726</v>
+        <v>-2.2272</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5365</v>
+        <v>-0.6982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7361</v>
+        <v>-1.529</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6445</v>
+        <v>0.8593</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4955</v>
+        <v>0.9599</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1489</v>
+        <v>-0.1006</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1762</v>
+        <v>-3.2546</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4302</v>
+        <v>-2.541</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.746</v>
+        <v>-0.7137</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.5982</v>
+        <v>-2.9674</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8368</v>
+        <v>-0.1199</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.7614</v>
+        <v>-2.8475</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.371</v>
+        <v>-1.3658</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1386</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.2324</v>
+        <v>-2.0044</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2272</v>
+        <v>-1.6016</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6982</v>
+        <v>-0.7584</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.529</v>
+        <v>-0.8431</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.3917</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.3195</v>
-      </c>
       <c r="S9" t="n">
-        <v>0.7442</v>
+        <v>0.4808</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0464</v>
+        <v>-0.0154</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3022</v>
+        <v>0.4962</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7501</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.5361</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6586</v>
+        <v>-3.382</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7769</v>
+        <v>-2.3894</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8817</v>
+        <v>-0.9925</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9674</v>
+        <v>-2.526</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1199</v>
+        <v>-1.7899</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8475</v>
+        <v>-0.7361</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3658</v>
+        <v>-1.2534</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6385999999999999</v>
+        <v>-1.2534</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0044</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6016</v>
+        <v>-1.2726</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7584</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8431</v>
+        <v>-0.7361</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0769</v>
+        <v>0.0718</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2513</v>
+        <v>0.0237</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3282</v>
+        <v>0.0481</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4589</v>
+        <v>-4.0964</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6548</v>
+        <v>-2.3259</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8041</v>
+        <v>-1.7705</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8684</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4282</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0139</v>
+        <v>0.315</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4143</v>
+        <v>-0.3806</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.7544</v>
+        <v>-14.0075</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.051</v>
+        <v>-9.304200000000002</v>
       </c>
       <c r="F12" t="n">
         <v>-4.7034</v>
@@ -1369,7 +1369,7 @@
         <v>-5.998900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.0067</v>
+        <v>-6.006700000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-13.9782</v>
@@ -1378,7 +1378,7 @@
         <v>-6.0656</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.912499999999999</v>
+        <v>-7.912500000000001</v>
       </c>
       <c r="P12" t="n">
         <v>4.6392</v>
@@ -1390,10 +1390,10 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>3.343</v>
+        <v>4.0897</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1657</v>
+        <v>2.9126</v>
       </c>
       <c r="U12" t="n">
         <v>1.1774</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7873</v>
+        <v>5.4949</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0851</v>
+        <v>1.5849</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7022</v>
+        <v>3.91</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9815</v>
+        <v>5.0302</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8425</v>
+        <v>2.0791</v>
       </c>
       <c r="I13" t="n">
-        <v>4.139</v>
+        <v>2.9512</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8265</v>
+        <v>2.5607</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1532</v>
+        <v>0.9179</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6733</v>
+        <v>1.6428</v>
       </c>
       <c r="M13" t="n">
-        <v>2.155</v>
+        <v>2.4695</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6893</v>
+        <v>1.1611</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4657</v>
+        <v>1.3084</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6761</v>
+        <v>-0.1436</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0455</v>
+        <v>-0.4244</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3695</v>
+        <v>0.2807</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3725</v>
+        <v>4.8273</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1131</v>
+        <v>3.2031</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2594</v>
+        <v>1.6242</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0302</v>
+        <v>5.9815</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0791</v>
+        <v>1.8425</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9512</v>
+        <v>4.139</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5607</v>
+        <v>3.8265</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9179</v>
+        <v>1.1532</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6428</v>
+        <v>2.6733</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4695</v>
+        <v>2.155</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1611</v>
+        <v>0.6893</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3084</v>
+        <v>1.4657</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2661</v>
+        <v>-0.6361</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8962</v>
+        <v>-0.9276</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3699</v>
+        <v>0.2915</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1658</v>
+        <v>3.7144</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4866</v>
+        <v>3.2517</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6792</v>
+        <v>0.4627</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9289</v>
+        <v>4.6294</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9953</v>
+        <v>1.5378</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9336</v>
+        <v>3.0916</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5756</v>
+        <v>4.3405</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4284</v>
+        <v>1.6672</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1472</v>
+        <v>2.6733</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3532</v>
+        <v>0.2889</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4331</v>
+        <v>-0.1294</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7863</v>
+        <v>0.4183</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6623</v>
+        <v>0.0127</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9109</v>
+        <v>0.0709</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2486</v>
+        <v>-0.0582</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8897</v>
+        <v>3.5701</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9938</v>
+        <v>0.4041</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8958</v>
+        <v>3.166</v>
       </c>
       <c r="G16" t="n">
         <v>3.9965</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4472</v>
+        <v>0.1276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5272</v>
+        <v>-0.0626</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0799</v>
+        <v>0.1902</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3497</v>
+        <v>3.0421</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3696</v>
+        <v>2.0712</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0199</v>
+        <v>0.9709</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6294</v>
+        <v>1.9289</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5378</v>
+        <v>0.9953</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0916</v>
+        <v>0.9336</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3405</v>
+        <v>1.5756</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6672</v>
+        <v>1.4284</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6733</v>
+        <v>0.1472</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2889</v>
+        <v>0.3532</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1294</v>
+        <v>-0.4331</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>0.7863</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3519</v>
+        <v>0.5386</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1889</v>
+        <v>0.4955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5407999999999999</v>
+        <v>0.0431</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2001</v>
+        <v>0.5856</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9287</v>
+        <v>-0.6928</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7287</v>
+        <v>1.2785</v>
       </c>
       <c r="G18" t="n">
         <v>0.339</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2349</v>
+        <v>-0.4492</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3387</v>
+        <v>0.2111</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9822</v>
+        <v>-0.0544</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7845</v>
+        <v>1.6102</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7667</v>
+        <v>-1.6646</v>
       </c>
       <c r="G19" t="n">
         <v>2.488</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8799</v>
+        <v>0.0479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7468</v>
+        <v>0.0788</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1331</v>
+        <v>-0.031</v>
       </c>
       <c r="V19" t="n">
         <v>-2.8223</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3375</v>
+        <v>-0.9791</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8494</v>
+        <v>-2.3352</v>
       </c>
       <c r="F20" t="n">
-        <v>1.512</v>
+        <v>1.356</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9324</v>
+        <v>-0.8425</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9186</v>
+        <v>0.1512</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0138</v>
+        <v>-0.9937</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2995</v>
+        <v>-1.0891</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3865</v>
+        <v>-0.4131</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0871</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6329</v>
+        <v>0.2466</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5321</v>
+        <v>0.5644</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1009</v>
+        <v>-0.3178</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8782</v>
+        <v>0.5592</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5975</v>
+        <v>0.1456</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2807</v>
+        <v>0.4136</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3437</v>
+        <v>-1.1288</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2172</v>
+        <v>-2.4956</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.3668</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8425</v>
+        <v>1.9324</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1512</v>
+        <v>0.9186</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9937</v>
+        <v>1.0138</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0891</v>
+        <v>0.2995</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4131</v>
+        <v>0.3865</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.0871</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2466</v>
+        <v>1.6329</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5644</v>
+        <v>0.5321</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3178</v>
+        <v>1.1009</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1946</v>
+        <v>-0.6695</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>-0.2436</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.4259</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9472</v>
+        <v>-1.1723</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1341</v>
+        <v>-1.8982</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1869</v>
+        <v>0.7259</v>
       </c>
       <c r="G22" t="n">
         <v>0.5006</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3602</v>
+        <v>0.4147</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1142</v>
+        <v>0.3501</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4744</v>
+        <v>0.0646</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.7543</v>
+        <v>17.8998</v>
       </c>
       <c r="E23" t="n">
-        <v>4.703299999999999</v>
+        <v>4.703399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>10.0511</v>
+        <v>13.1964</v>
       </c>
       <c r="G23" t="n">
         <v>25.984</v>
@@ -2224,7 +2224,7 @@
         <v>13.9779</v>
       </c>
       <c r="K23" t="n">
-        <v>6.0657</v>
+        <v>6.065700000000001</v>
       </c>
       <c r="L23" t="n">
         <v>7.912299999999999</v>
@@ -2233,7 +2233,7 @@
         <v>12.0059</v>
       </c>
       <c r="N23" t="n">
-        <v>5.999000000000001</v>
+        <v>5.999</v>
       </c>
       <c r="O23" t="n">
         <v>6.0069</v>
@@ -2245,16 +2245,16 @@
         <v>-11.5978</v>
       </c>
       <c r="R23" t="n">
-        <v>6.9588</v>
+        <v>6.958799999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.3432</v>
+        <v>-0.1977000000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1774</v>
+        <v>-1.1776</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.1656</v>
+        <v>0.9797000000000002</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2477</v>
